--- a/data/carriers_data/naphtha_bio/naphtha_bio_availability.xlsx
+++ b/data/carriers_data/naphtha_bio/naphtha_bio_availability.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\data\carriers_data\naphtha_bio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5440B357-0258-4391-A339-7AD2CF864BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6FD398-D18D-4667-B2E4-E0B1AE6847C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16620" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="note" sheetId="2" r:id="rId1"/>
-    <sheet name="availability" sheetId="1" r:id="rId2"/>
+    <sheet name="availability_low" sheetId="1" r:id="rId2"/>
+    <sheet name="availability_high" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
   <si>
     <t>BE</t>
   </si>
@@ -46,9 +47,6 @@
   </si>
   <si>
     <t>NL</t>
-  </si>
-  <si>
-    <t>Weights on availability (source: https://en.wikipedia.org/wiki/List_of_countries_by_natural_gas_consumption)</t>
   </si>
   <si>
     <t>EU</t>
@@ -90,9 +88,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -373,41 +370,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B073FAB7-2B07-4271-9F03-B0CE1B920C01}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0.1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -422,7 +390,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="C1">
         <v>2030</v>
@@ -439,20 +407,20 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <f>note!$B5*availability!B$5</f>
-        <v>50</v>
+        <f>20%*B5</f>
+        <v>30</v>
       </c>
       <c r="C2">
-        <f>note!$B$5*availability!C$5</f>
-        <v>50</v>
+        <f t="shared" ref="C2:E2" si="0">20%*C5</f>
+        <v>30</v>
       </c>
       <c r="D2">
-        <f>note!$B$5*availability!D$5</f>
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>60</v>
       </c>
       <c r="E2">
-        <f>note!$B$5*availability!E$5</f>
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -460,20 +428,20 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <f>note!$B6*availability!B$5</f>
-        <v>50</v>
+        <f>40%*B5</f>
+        <v>60</v>
       </c>
       <c r="C3">
-        <f>note!$B$5*availability!C$5</f>
-        <v>50</v>
+        <f t="shared" ref="C3:E3" si="1">40%*C5</f>
+        <v>60</v>
       </c>
       <c r="D3">
-        <f>note!$B$5*availability!D$5</f>
-        <v>100</v>
+        <f t="shared" si="1"/>
+        <v>120</v>
       </c>
       <c r="E3">
-        <f>note!$B$5*availability!E$5</f>
-        <v>100</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -481,37 +449,142 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <f>note!$B7*availability!B$5</f>
-        <v>50</v>
+        <f>40%*B5</f>
+        <v>60</v>
       </c>
       <c r="C4">
-        <f>note!$B$5*availability!C$5</f>
-        <v>50</v>
+        <f t="shared" ref="C4:E4" si="2">40%*C5</f>
+        <v>60</v>
       </c>
       <c r="D4">
-        <f>note!$B$5*availability!D$5</f>
-        <v>100</v>
+        <f t="shared" si="2"/>
+        <v>120</v>
       </c>
       <c r="E4">
-        <f>note!$B$5*availability!E$5</f>
-        <v>100</v>
+        <f t="shared" si="2"/>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="C5">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="D5">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="E5">
-        <v>1000</v>
+        <v>450</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A7879C-C6F4-4FD3-9D39-D2B408CBAAA4}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1">
+        <v>2025</v>
+      </c>
+      <c r="C1">
+        <v>2030</v>
+      </c>
+      <c r="D1">
+        <v>2040</v>
+      </c>
+      <c r="E1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <f>20%*B5</f>
+        <v>30</v>
+      </c>
+      <c r="C2">
+        <f t="shared" ref="C2:E2" si="0">20%*C5</f>
+        <v>30</v>
+      </c>
+      <c r="D2">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="E2">
+        <f t="shared" si="0"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <f>40%*B5</f>
+        <v>60</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:E3" si="1">40%*C5</f>
+        <v>60</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="1"/>
+        <v>210</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>40%*B5</f>
+        <v>60</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:E4" si="2">40%*C5</f>
+        <v>60</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="2"/>
+        <v>210</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="2"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>150</v>
+      </c>
+      <c r="C5">
+        <v>150</v>
+      </c>
+      <c r="D5">
+        <f>AVERAGE(C5,E5)</f>
+        <v>525</v>
+      </c>
+      <c r="E5">
+        <v>900</v>
       </c>
     </row>
   </sheetData>

--- a/data/carriers_data/naphtha_bio/naphtha_bio_availability.xlsx
+++ b/data/carriers_data/naphtha_bio/naphtha_bio_availability.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\data\carriers_data\naphtha_bio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6FD398-D18D-4667-B2E4-E0B1AE6847C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A157F25-E460-4EB7-A830-BA1E9E60FDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="note" sheetId="2" r:id="rId1"/>

--- a/data/carriers_data/naphtha_bio/naphtha_bio_availability.xlsx
+++ b/data/carriers_data/naphtha_bio/naphtha_bio_availability.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A157F25-E460-4EB7-A830-BA1E9E60FDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16620" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="note" sheetId="2" r:id="rId1"/>
